--- a/artfynd/A 57409-2021 artfynd.xlsx
+++ b/artfynd/A 57409-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57409-2021 artfynd.xlsx
+++ b/artfynd/A 57409-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96676497</v>
+        <v>64892153</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +710,16 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Fårviken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811014.6516921299</v>
+        <v>810577</v>
       </c>
       <c r="R2" t="n">
-        <v>7171429.752581226</v>
+        <v>7171038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,22 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96676541</v>
+        <v>64892211</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +790,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,17 +814,16 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Fårviken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811009.9835514531</v>
+        <v>810576</v>
       </c>
       <c r="R3" t="n">
-        <v>7171424.506214393</v>
+        <v>7171043</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,37 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96676552</v>
+        <v>64139119</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,20 +918,19 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Storön 3, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811024.7145265916</v>
+        <v>810601</v>
       </c>
       <c r="R4" t="n">
-        <v>7171424.718796491</v>
+        <v>7171360</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96676600</v>
+        <v>96676497</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1082,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810985.1673918737</v>
+        <v>811015</v>
       </c>
       <c r="R5" t="n">
-        <v>7171404.190065147</v>
+        <v>7171430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,19 +1062,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100945608</v>
+        <v>96676541</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,34 +1103,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,13 +1134,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811004.9739228553</v>
+        <v>811010</v>
       </c>
       <c r="R6" t="n">
-        <v>7171401.456726377</v>
+        <v>7171425</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,22 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100736336</v>
+        <v>96676600</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810985.0352958039</v>
+        <v>810985</v>
       </c>
       <c r="R7" t="n">
-        <v>7171405.4766043</v>
+        <v>7171404</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,19 +1272,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,6 +1299,750 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100736336</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>810985</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7171405</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96676552</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>811025</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7171425</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100945608</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>811005</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7171402</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122649921</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>810786</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7171426</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122649959</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>810845</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7171445</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122649988</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>810939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7171498</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122649934</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>810828</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7171441</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57409-2021 artfynd.xlsx
+++ b/artfynd/A 57409-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64892153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64892211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64139119</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96676497</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96676541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96676600</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100736336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96676552</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945608</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122649921</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122649959</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1933,6 +1993,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122649988</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,8 +2108,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122649934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>